--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486924_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486924_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1941</v>
+        <v>5.7515</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6157</v>
+        <v>5.1407</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5784</v>
+        <v>0.6108</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1341</v>
+        <v>5.9366</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4129</v>
+        <v>2.4268</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7211</v>
+        <v>3.5098</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7832</v>
+        <v>6.4302</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9939</v>
+        <v>3.063</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7893</v>
+        <v>3.3673</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3509</v>
+        <v>-0.4936</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.581</v>
+        <v>-0.6362</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9318</v>
+        <v>0.1425</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7664</v>
+        <v>-0.1501</v>
       </c>
       <c r="T2" t="n">
-        <v>0.736</v>
+        <v>-0.4496</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0304</v>
+        <v>0.2995</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9384</v>
+        <v>-0.2402</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6982</v>
+        <v>1.4189</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2402</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.255</v>
+        <v>5.6777</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9702</v>
+        <v>4.1586</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2848</v>
+        <v>1.5191</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9366</v>
+        <v>5.1341</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4268</v>
+        <v>3.4129</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5098</v>
+        <v>1.7211</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4302</v>
+        <v>4.7832</v>
       </c>
       <c r="K3" t="n">
-        <v>3.063</v>
+        <v>3.9939</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3673</v>
+        <v>0.7893</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4936</v>
+        <v>0.3509</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6362</v>
+        <v>-0.581</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1425</v>
+        <v>0.9318</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4641</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6201</v>
+        <v>0.2788</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0266</v>
+        <v>-0.0289</v>
       </c>
       <c r="V3" t="n">
+        <v>-0.9384</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.6982</v>
+      </c>
+      <c r="X3" t="n">
         <v>-0.2402</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.4189</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.6591</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5537</v>
+        <v>-0.172</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7719</v>
+        <v>-2.4382</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3255</v>
+        <v>2.2662</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4103</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.929</v>
+        <v>0.2034</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5189</v>
+        <v>-0.1475</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4102</v>
+        <v>0.3509</v>
       </c>
       <c r="V4" t="n">
         <v>0.2402</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0773</v>
+        <v>-1.3823</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.4144</v>
+        <v>-1.4939</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3371</v>
+        <v>0.1116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6297</v>
+        <v>2.9653</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5374</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9077</v>
+        <v>1.992</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9678</v>
+        <v>2.2566</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8103</v>
+        <v>0.9412</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8425</v>
+        <v>1.3154</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3381</v>
+        <v>0.7087</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2729</v>
+        <v>0.0321</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.6766</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.2321</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.3122</v>
+        <v>-3.2855</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0801</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7037</v>
+        <v>-0.1075</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3102</v>
+        <v>-0.4651</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0139</v>
+        <v>0.3576</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>-2.5975</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4189</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0602</v>
+        <v>-1.7229</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0828</v>
+        <v>-3.3486</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0227</v>
+        <v>1.6257</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9653</v>
+        <v>0.6297</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.5374</v>
       </c>
       <c r="I6" t="n">
-        <v>1.992</v>
+        <v>-0.9077</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2566</v>
+        <v>0.9678</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9412</v>
+        <v>1.8103</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3154</v>
+        <v>-0.8425</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7087</v>
+        <v>-0.3381</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0321</v>
+        <v>-0.2729</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6766</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6427</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.2855</v>
+        <v>-4.3122</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>3.0801</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7853</v>
+        <v>0.0581</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.054</v>
+        <v>-0.2444</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2687</v>
+        <v>0.3025</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.5975</v>
+        <v>-1.1786</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.5975</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4818</v>
+        <v>-2.3476</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8998</v>
+        <v>-1.7952</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.582</v>
+        <v>-0.5524</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8731</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2515</v>
+        <v>-0.1172</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1976</v>
+        <v>-0.093</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0538</v>
+        <v>-0.0242</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1786</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7541</v>
+        <v>-2.7244</v>
       </c>
       <c r="E8" t="n">
         <v>-2.2522</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5019</v>
+        <v>-0.4722</v>
       </c>
       <c r="G8" t="n">
         <v>-3.0907</v>
@@ -1078,13 +1078,13 @@
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3677</v>
+        <v>-0.3381</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0854</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2824</v>
+        <v>-0.2527</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9384</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5668</v>
+        <v>-3.389</v>
       </c>
       <c r="E9" t="n">
         <v>-2.6878</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.879</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0.5472</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.3468</v>
       </c>
       <c r="T9" t="n">
         <v>-0.4806</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0441</v>
+        <v>0.1338</v>
       </c>
       <c r="V9" t="n">
         <v>-2.3573</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.5801</v>
+        <v>-5.8793</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1736</v>
+        <v>-5.6506</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4065</v>
+        <v>-0.2286</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7766</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1794</v>
+        <v>-0.4785</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7169</v>
+        <v>-0.1939</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4625</v>
+        <v>-0.2846</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0082</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5175</v>
+        <v>-6.188300000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.6966</v>
+        <v>-10.3672</v>
       </c>
       <c r="F11" t="n">
-        <v>4.179099999999999</v>
+        <v>4.1791</v>
       </c>
       <c r="G11" t="n">
         <v>7.062200000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3.456700000000001</v>
+        <v>3.4567</v>
       </c>
       <c r="I11" t="n">
         <v>3.605300000000001</v>
@@ -1288,10 +1288,10 @@
         <v>6.936500000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>4.400000000000002</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5368</v>
+        <v>2.536799999999999</v>
       </c>
       <c r="M11" t="n">
         <v>0.1256999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>16.4273</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3562</v>
+        <v>-1.0267</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.2099</v>
+        <v>-1.8807</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8538</v>
+        <v>0.8538999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-11.197</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.8373</v>
+        <v>9.165900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5157</v>
+        <v>5.9341</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3217</v>
+        <v>3.2318</v>
       </c>
       <c r="G12" t="n">
         <v>2.0043</v>
@@ -1390,13 +1390,13 @@
         <v>2.6694</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3538</v>
+        <v>-0.0252</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6782</v>
+        <v>-0.2598</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6756</v>
+        <v>0.2346</v>
       </c>
       <c r="V12" t="n">
         <v>5.5441</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2894</v>
+        <v>3.6521</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3171</v>
+        <v>0.4217</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9723</v>
+        <v>3.2303</v>
       </c>
       <c r="G13" t="n">
         <v>0.0046</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5447</v>
+        <v>-0.1821</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.5814</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1413</v>
+        <v>0.3993</v>
       </c>
       <c r="V13" t="n">
         <v>2.5975</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.234</v>
+        <v>1.6064</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4611</v>
+        <v>-0.1666</v>
       </c>
       <c r="F14" t="n">
         <v>1.773</v>
@@ -1546,10 +1546,10 @@
         <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3288</v>
+        <v>0.7012</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1389</v>
+        <v>0.5113</v>
       </c>
       <c r="U14" t="n">
         <v>0.1899</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3105</v>
+        <v>0.7786</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7218</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0323</v>
+        <v>1.2913</v>
       </c>
       <c r="G15" t="n">
         <v>0.899</v>
@@ -1624,13 +1624,13 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1528</v>
+        <v>0.6209</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1513</v>
+        <v>0.0579</v>
       </c>
       <c r="U15" t="n">
-        <v>1.304</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-1.7679</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9051</v>
+        <v>0.354</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8127</v>
+        <v>-2.0704</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9075</v>
+        <v>2.4243</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.4675</v>
+        <v>-2.3035</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.541</v>
+        <v>-1.3138</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9265</v>
+        <v>-0.9897</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2309</v>
+        <v>-2.7731</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-1.1543</v>
       </c>
       <c r="L16" t="n">
-        <v>0.302</v>
+        <v>-1.6188</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6984</v>
+        <v>0.4696</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.47</v>
+        <v>-0.1596</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2284</v>
+        <v>0.6291</v>
       </c>
       <c r="P16" t="n">
-        <v>0.616</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6427</v>
+        <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2289</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8405</v>
+        <v>0.3989</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3884</v>
+        <v>0.3818</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5277</v>
+        <v>1.8768</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7679</v>
+        <v>2.3573</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0521</v>
+        <v>-0.0159</v>
       </c>
       <c r="E17" t="n">
         <v>-1.0737</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1258</v>
+        <v>1.0577</v>
       </c>
       <c r="G17" t="n">
         <v>0.2089</v>
@@ -1780,13 +1780,13 @@
         <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>0.718</v>
+        <v>0.65</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0931</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8111</v>
+        <v>0.7431</v>
       </c>
       <c r="V17" t="n">
         <v>1.1786</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7375</v>
+        <v>-0.4826</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4888</v>
+        <v>0.662</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7513</v>
+        <v>-1.1446</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3035</v>
+        <v>-2.4675</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3138</v>
+        <v>-1.541</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9897</v>
+        <v>-0.9265</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.7731</v>
+        <v>0.2309</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1543</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.6188</v>
+        <v>0.302</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4696</v>
+        <v>-2.6984</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1596</v>
+        <v>-1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6291</v>
+        <v>-1.2284</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0.616</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3107</v>
+        <v>-0.1589</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0195</v>
+        <v>-0.3101</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2912</v>
+        <v>0.1513</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8768</v>
+        <v>1.5277</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3573</v>
+        <v>1.7679</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4805</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.05</v>
+        <v>-0.8374</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1978</v>
+        <v>-2.5701</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1478</v>
+        <v>1.7328</v>
       </c>
       <c r="G19" t="n">
         <v>0.5795</v>
@@ -1936,13 +1936,13 @@
         <v>2.4641</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3153</v>
+        <v>-0.1027</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9145</v>
+        <v>-0.2869</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5992</v>
+        <v>0.1842</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6982</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.533</v>
+        <v>-1.5572</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7847</v>
+        <v>-0.1768</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2517</v>
+        <v>-1.3804</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9906</v>
+        <v>-1.0458</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3117</v>
+        <v>-0.9247</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.679</v>
+        <v>-0.1211</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0334</v>
+        <v>0.664</v>
       </c>
       <c r="K20" t="n">
         <v>0.0195</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0529</v>
+        <v>0.6445</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-1.7098</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3311</v>
+        <v>-0.9442</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6261</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P20" t="n">
         <v>-0.8214</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2789</v>
+        <v>0.0697</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3021</v>
+        <v>-0.0543</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0232</v>
+        <v>0.124</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.885</v>
+        <v>-1.7074</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.386</v>
+        <v>-2.0985</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.499</v>
+        <v>0.3911</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0458</v>
+        <v>-0.9906</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9247</v>
+        <v>-0.3117</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1211</v>
+        <v>-0.679</v>
       </c>
       <c r="J21" t="n">
-        <v>0.664</v>
+        <v>-0.0334</v>
       </c>
       <c r="K21" t="n">
         <v>0.0195</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6445</v>
+        <v>-0.0529</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7098</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9442</v>
+        <v>-0.3311</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.6261</v>
       </c>
       <c r="P21" t="n">
         <v>-0.8214</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.258</v>
+        <v>0.1046</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2635</v>
+        <v>-0.0117</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0054</v>
+        <v>0.1163</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9055</v>
+        <v>-3.7416</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6329</v>
+        <v>-2.5283</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2726</v>
+        <v>-1.2133</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1314</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5688</v>
+        <v>-0.4049</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3294</v>
+        <v>-0.2248</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2394</v>
+        <v>-0.1801</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.5174</v>
+        <v>7.214900000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1791</v>
+        <v>-4.1792</v>
       </c>
       <c r="F23" t="n">
-        <v>10.6968</v>
+        <v>11.394</v>
       </c>
       <c r="G23" t="n">
         <v>-7.062200000000001</v>
@@ -2224,7 +2224,7 @@
         <v>-0.1255999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9432999999999998</v>
+        <v>0.9432999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>-1.0688</v>
@@ -2248,13 +2248,13 @@
         <v>17.454</v>
       </c>
       <c r="S23" t="n">
-        <v>1.356100000000001</v>
+        <v>2.0533</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.854</v>
+        <v>-0.8540000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2099</v>
+        <v>2.9074</v>
       </c>
       <c r="V23" t="n">
         <v>11.197</v>
